--- a/storage/app/public/vocabs/paleomagnetism/1.3/paleomagnetism_1-3.xlsx
+++ b/storage/app/public/vocabs/paleomagnetism/1.3/paleomagnetism_1-3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="535">
   <si>
     <t>synonyms</t>
   </si>
@@ -1179,6 +1179,51 @@
   </si>
   <si>
     <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters</t>
+  </si>
+  <si>
+    <t>coercive force</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-coercive_force</t>
+  </si>
+  <si>
+    <t>bias exchange field</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-bias_exchange_field</t>
+  </si>
+  <si>
+    <t>remanent coercive force</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-remanent_coercive_force</t>
+  </si>
+  <si>
+    <t>saturation magnetisation</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-saturation_magnetisation</t>
+  </si>
+  <si>
+    <t>saturation remanence</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-saturation_remanence</t>
+  </si>
+  <si>
+    <t>high-field susceptibility</t>
+  </si>
+  <si>
+    <t>#high field susceptibility</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-high-field_susceptibility</t>
+  </si>
+  <si>
+    <t>hysteresis shape parameter</t>
+  </si>
+  <si>
+    <t>https://epos-msl.uu.nl/voc/paleomagnetism/1.3/measured_property-magnetic_hysteresis_curves-hysteresis_parameters-hysteresis_shape_parameter</t>
   </si>
   <si>
     <t>first order reversal curve (FORC)</t>
@@ -1914,7 +1959,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I207"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3431,189 +3476,189 @@
       </c>
     </row>
     <row r="153" spans="1:9">
-      <c r="B153" t="s">
+      <c r="D153" t="s">
         <v>388</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>389</v>
       </c>
-      <c r="G153" t="s">
+    </row>
+    <row r="154" spans="1:9">
+      <c r="D154" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="154" spans="1:9">
-      <c r="B154" t="s">
+      <c r="G154" t="s">
         <v>391</v>
       </c>
-      <c r="F154" t="s">
+    </row>
+    <row r="155" spans="1:9">
+      <c r="D155" t="s">
         <v>392</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G155" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
-      <c r="C155" t="s">
+    <row r="156" spans="1:9">
+      <c r="D156" t="s">
         <v>394</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G156" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
-      <c r="C156" t="s">
+    <row r="157" spans="1:9">
+      <c r="D157" t="s">
         <v>396</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G157" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
-      <c r="B157" t="s">
+    <row r="158" spans="1:9">
+      <c r="D158" t="s">
         <v>398</v>
       </c>
-      <c r="G157" t="s">
+      <c r="F158" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="158" spans="1:9">
-      <c r="C158" t="s">
+      <c r="G158" t="s">
         <v>400</v>
       </c>
-      <c r="G158" t="s">
+    </row>
+    <row r="159" spans="1:9">
+      <c r="D159" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="159" spans="1:9">
-      <c r="C159" t="s">
+      <c r="G159" t="s">
         <v>402</v>
       </c>
-      <c r="F159" t="s">
+    </row>
+    <row r="160" spans="1:9">
+      <c r="B160" t="s">
         <v>403</v>
       </c>
-      <c r="G159" t="s">
+      <c r="F160" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="160" spans="1:9">
-      <c r="C160" t="s">
+      <c r="G160" t="s">
         <v>405</v>
       </c>
-      <c r="F160" t="s">
+    </row>
+    <row r="161" spans="1:9">
+      <c r="B161" t="s">
         <v>406</v>
       </c>
-      <c r="G160" t="s">
+      <c r="F161" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="161" spans="1:9">
-      <c r="C161" t="s">
+      <c r="G161" t="s">
         <v>408</v>
-      </c>
-      <c r="F161" t="s">
-        <v>409</v>
-      </c>
-      <c r="G161" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="C162" t="s">
-        <v>411</v>
-      </c>
-      <c r="F162" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G162" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="C163" t="s">
+        <v>411</v>
+      </c>
+      <c r="G163" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="B164" t="s">
+        <v>413</v>
+      </c>
+      <c r="G164" t="s">
         <v>414</v>
       </c>
-      <c r="F163" t="s">
+    </row>
+    <row r="165" spans="1:9">
+      <c r="C165" t="s">
         <v>415</v>
       </c>
-      <c r="G163" t="s">
+      <c r="G165" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
-      <c r="C164" t="s">
+    <row r="166" spans="1:9">
+      <c r="C166" t="s">
         <v>417</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F166" t="s">
         <v>418</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G166" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
-      <c r="B165" t="s">
+    <row r="167" spans="1:9">
+      <c r="C167" t="s">
         <v>420</v>
       </c>
-      <c r="F165" t="s">
+      <c r="F167" t="s">
         <v>421</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G167" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
-      <c r="B166" t="s">
+    <row r="168" spans="1:9">
+      <c r="C168" t="s">
         <v>423</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F168" t="s">
         <v>424</v>
       </c>
-      <c r="G166" t="s">
+      <c r="G168" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9">
-      <c r="A167" t="s">
-        <v>426</v>
-      </c>
-      <c r="G167" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9">
-      <c r="B168" t="s">
-        <v>428</v>
-      </c>
-      <c r="G168" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="C169" t="s">
+        <v>426</v>
+      </c>
+      <c r="F169" t="s">
+        <v>427</v>
+      </c>
+      <c r="G169" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="C170" t="s">
+        <v>429</v>
+      </c>
+      <c r="F170" t="s">
         <v>430</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G170" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
-      <c r="D170" t="s">
+    <row r="171" spans="1:9">
+      <c r="C171" t="s">
         <v>432</v>
       </c>
-      <c r="G170" t="s">
+      <c r="F171" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="171" spans="1:9">
-      <c r="D171" t="s">
+      <c r="G171" t="s">
         <v>434</v>
       </c>
-      <c r="G171" t="s">
+    </row>
+    <row r="172" spans="1:9">
+      <c r="B172" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="172" spans="1:9">
-      <c r="D172" t="s">
+      <c r="F172" t="s">
         <v>436</v>
       </c>
       <c r="G172" t="s">
@@ -3621,34 +3666,34 @@
       </c>
     </row>
     <row r="173" spans="1:9">
-      <c r="D173" t="s">
+      <c r="B173" t="s">
         <v>438</v>
       </c>
+      <c r="F173" t="s">
+        <v>439</v>
+      </c>
       <c r="G173" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:9">
-      <c r="C174" t="s">
-        <v>440</v>
+      <c r="A174" t="s">
+        <v>441</v>
       </c>
       <c r="G174" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:9">
-      <c r="C175" t="s">
-        <v>442</v>
+      <c r="B175" t="s">
+        <v>443</v>
       </c>
       <c r="G175" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="C176" t="s">
-        <v>444</v>
-      </c>
-      <c r="F176" t="s">
         <v>445</v>
       </c>
       <c r="G176" t="s">
@@ -3656,132 +3701,132 @@
       </c>
     </row>
     <row r="177" spans="1:9">
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>447</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>448</v>
       </c>
-      <c r="G177" t="s">
+    </row>
+    <row r="178" spans="1:9">
+      <c r="D178" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="178" spans="1:9">
-      <c r="C178" t="s">
+      <c r="G178" t="s">
         <v>450</v>
       </c>
-      <c r="F178" t="s">
+    </row>
+    <row r="179" spans="1:9">
+      <c r="D179" t="s">
         <v>451</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G179" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
-      <c r="C179" t="s">
+    <row r="180" spans="1:9">
+      <c r="D180" t="s">
         <v>453</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G180" t="s">
         <v>454</v>
-      </c>
-      <c r="G179" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
-      <c r="C180" t="s">
-        <v>456</v>
-      </c>
-      <c r="F180" t="s">
-        <v>457</v>
-      </c>
-      <c r="G180" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="C181" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G181" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="C182" t="s">
-        <v>461</v>
-      </c>
-      <c r="F182" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G182" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="C183" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F183" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G183" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="C184" t="s">
-        <v>467</v>
+        <v>462</v>
+      </c>
+      <c r="F184" t="s">
+        <v>463</v>
       </c>
       <c r="G184" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="C185" t="s">
+        <v>465</v>
+      </c>
+      <c r="F185" t="s">
+        <v>466</v>
+      </c>
+      <c r="G185" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="C186" t="s">
+        <v>468</v>
+      </c>
+      <c r="F186" t="s">
         <v>469</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G186" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9">
-      <c r="B186" t="s">
-        <v>471</v>
-      </c>
-      <c r="G186" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="C187" t="s">
+        <v>471</v>
+      </c>
+      <c r="F187" t="s">
+        <v>472</v>
+      </c>
+      <c r="G187" t="s">
         <v>473</v>
-      </c>
-      <c r="G187" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="C188" t="s">
+        <v>474</v>
+      </c>
+      <c r="G188" t="s">
         <v>475</v>
-      </c>
-      <c r="G188" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="C189" t="s">
+        <v>476</v>
+      </c>
+      <c r="F189" t="s">
         <v>477</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>478</v>
-      </c>
-      <c r="G189" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="C190" t="s">
+        <v>479</v>
+      </c>
+      <c r="F190" t="s">
         <v>480</v>
       </c>
       <c r="G190" t="s">
@@ -3792,66 +3837,66 @@
       <c r="C191" t="s">
         <v>482</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>483</v>
-      </c>
-      <c r="G191" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="C192" t="s">
+        <v>484</v>
+      </c>
+      <c r="G192" t="s">
         <v>485</v>
       </c>
-      <c r="G192" t="s">
+    </row>
+    <row r="193" spans="1:9">
+      <c r="B193" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="193" spans="1:9">
-      <c r="C193" t="s">
+      <c r="G193" t="s">
         <v>487</v>
-      </c>
-      <c r="G193" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="C194" t="s">
+        <v>488</v>
+      </c>
+      <c r="G194" t="s">
         <v>489</v>
-      </c>
-      <c r="G194" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="C195" t="s">
+        <v>490</v>
+      </c>
+      <c r="G195" t="s">
         <v>491</v>
       </c>
-      <c r="G195" t="s">
+    </row>
+    <row r="196" spans="1:9">
+      <c r="C196" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="196" spans="1:9">
-      <c r="B196" t="s">
+      <c r="F196" t="s">
         <v>493</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>494</v>
-      </c>
-      <c r="G196" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" t="s">
+        <v>495</v>
+      </c>
+      <c r="G197" t="s">
         <v>496</v>
-      </c>
-      <c r="G197" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" t="s">
+        <v>497</v>
+      </c>
+      <c r="F198" t="s">
         <v>498</v>
       </c>
       <c r="G198" t="s">
@@ -3886,16 +3931,13 @@
       <c r="C202" t="s">
         <v>506</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>507</v>
       </c>
-      <c r="G202" t="s">
+    </row>
+    <row r="203" spans="1:9">
+      <c r="B203" t="s">
         <v>508</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9">
-      <c r="C203" t="s">
-        <v>310</v>
       </c>
       <c r="F203" t="s">
         <v>509</v>
@@ -3932,11 +3974,73 @@
       <c r="C207" t="s">
         <v>517</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>518</v>
       </c>
-      <c r="G207" t="s">
+    </row>
+    <row r="208" spans="1:9">
+      <c r="C208" t="s">
         <v>519</v>
+      </c>
+      <c r="G208" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="C209" t="s">
+        <v>521</v>
+      </c>
+      <c r="F209" t="s">
+        <v>522</v>
+      </c>
+      <c r="G209" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="C210" t="s">
+        <v>310</v>
+      </c>
+      <c r="F210" t="s">
+        <v>524</v>
+      </c>
+      <c r="G210" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="C211" t="s">
+        <v>526</v>
+      </c>
+      <c r="G211" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="C212" t="s">
+        <v>528</v>
+      </c>
+      <c r="G212" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="C213" t="s">
+        <v>530</v>
+      </c>
+      <c r="G213" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="C214" t="s">
+        <v>532</v>
+      </c>
+      <c r="F214" t="s">
+        <v>533</v>
+      </c>
+      <c r="G214" t="s">
+        <v>534</v>
       </c>
     </row>
   </sheetData>
